--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,12 +436,12 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2814,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2864,1125 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1227,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1260,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1354,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1371,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1415,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1473,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1482,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1534,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1592,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1593,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1653,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1671,32 +1711,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1704,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,33 +1772,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1893,12 +1941,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1926,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,10 +1982,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2037,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2226,12 +2290,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq45推进至seq47，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2259,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,10 +2331,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq19（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2370,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3702,7 +3778,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3813,7 +3889,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3862,7 +3938,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -3928,7 +4004,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3986,6 +4062,922 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1830,32 +1830,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1863,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,33 +1891,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1974,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2068,32 +2076,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2101,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,33 +2137,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2267,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2295,7 +2311,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq45推进至seq47，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq45推进至seq58，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2323,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2779,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3001,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3112,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3461,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3667,7 +3683,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3794,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3905,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4020,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4135,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,7 +4250,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4365,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4460,7 +4476,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4575,7 +4591,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4629,7 +4645,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4706,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4805,7 +4821,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4859,7 +4875,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4936,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4974,7 +4990,348 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2195,32 +2195,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2256,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2272,13 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2429,32 +2437,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2462,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,33 +2498,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2628,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2739,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2873,32 +2889,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2906,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,33 +2950,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2984,32 +3008,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3017,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3041,33 +3069,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3239,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3350,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3461,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3683,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4304,7 +4336,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4397,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4508,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4530,7 +4562,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4623,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4645,7 +4677,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4738,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,7 +4853,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4875,7 +4907,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4968,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4990,7 +5022,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5083,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5105,7 +5137,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5198,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5210,13 +5242,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5313,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5331,7 +5367,685 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3127,32 +3127,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,33 +3188,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3238,32 +3246,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3271,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,33 +3307,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3460,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3493,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3537,13 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,32 +3706,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3715,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,33 +3767,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3904,32 +3936,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3937,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3961,17 +3997,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3981,12 +4017,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4052,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,7 +4242,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4249,32 +4285,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4282,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4306,37 +4346,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4404,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq53，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4397,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4405,10 +4445,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4508,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4562,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4590,32 +4646,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4623,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4647,17 +4707,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4667,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4892,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4907,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4968,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5022,7 +5082,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5137,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5252,7 +5312,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5367,7 +5427,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5593,7 +5653,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5765,7 +5825,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5876,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5930,7 +5990,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6051,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6040,12 +6100,813 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
           <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,22 +1549,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2152,22 +2152,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2518,17 +2518,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,13 +2633,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,7 +2754,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2861,7 +2865,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3337,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3452,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3682,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3912,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4413,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq53，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4437,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4503,7 +4507,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4564,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4596,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4608,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4773,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4798,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4822,37 +4834,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4892,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4913,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,17 +4953,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4957,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4995,32 +5011,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5028,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5052,17 +5072,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5072,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5110,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5143,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5167,17 +5191,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5187,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5225,32 +5249,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5258,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5282,17 +5310,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5302,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5340,32 +5368,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5373,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5397,37 +5429,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5455,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5488,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5512,17 +5548,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5532,13 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5566,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5599,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5623,17 +5667,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5643,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5764,7 +5808,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5864,7 +5908,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5875,7 +5919,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5990,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6105,7 +6149,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6220,7 +6264,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6331,7 +6375,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6446,7 +6490,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6561,7 +6605,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6676,7 +6720,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6791,7 +6835,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6896,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6896,17 +6940,691 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>14/28</t>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,13 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,13 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,13 +3454,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4326,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4864,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,14 +5218,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -5221,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5616,12 +5628,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5643,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5758,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5802,13 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5836,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5869,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,17 +5917,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5913,13 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5980,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6004,17 +6036,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6024,17 +6056,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6062,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6095,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6119,37 +6155,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6177,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6210,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6234,37 +6274,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6292,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6325,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6349,17 +6393,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6369,13 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6436,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6460,37 +6512,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6518,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6551,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6575,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6595,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6720,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6950,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7065,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7348,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7402,7 +7458,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7574,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7618,13 +7674,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,18 +2037,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2167,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,14 +2275,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -2286,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2643,7 +2647,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3808,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,14 +4032,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,14 +4746,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,14 +5341,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -5352,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5590,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6461,24 +6465,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6541,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6580,24 +6584,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,12 +6660,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6689,32 +6693,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6722,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,37 +6754,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6804,32 +6812,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6837,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6873,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6931,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6952,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,37 +6992,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7034,32 +7050,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7067,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,17 +7111,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7111,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7169,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7182,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,10 +7210,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7260,32 +7296,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7293,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,33 +7357,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7458,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7684,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7799,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7914,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7975,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8029,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8139,12 +8183,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8259,7 +8303,697 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2407,13 +2407,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2637,17 +2641,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,7 +2751,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2762,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,17 +2871,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3353,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,7 +3691,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3698,7 +3702,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3932,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4523,7 +4527,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4761,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4875,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5832,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7060,24 +7064,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7087,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7136,12 +7140,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7202,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,7 +7272,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7306,24 +7310,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7333,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7382,12 +7386,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7415,32 +7419,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7448,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,17 +7480,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7492,17 +7500,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7530,32 +7538,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7563,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,17 +7599,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7607,13 +7619,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7657,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7674,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,17 +7718,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7718,17 +7738,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7756,32 +7776,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7789,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7837,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7833,17 +7857,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7958,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8073,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8303,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8418,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8648,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8873,12 +8897,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8886,22 +8910,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8934,12 +8958,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8983,17 +9007,465 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>21/29</t>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,14 +1311,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,14 +1549,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3347,17 +3347,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>137.5</t>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,14 +7130,14 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7786,24 +7786,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7895,32 +7895,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7928,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7952,17 +7956,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7972,17 +7976,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8010,32 +8014,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8043,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8075,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8087,17 +8095,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8212,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8240,32 +8248,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8273,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,37 +8309,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8355,32 +8367,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8388,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8428,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8432,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8486,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8503,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,17 +8547,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8547,12 +8567,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8618,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8672,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8787,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8902,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9411,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9465,7 +9485,1042 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8133,32 +8133,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8166,7 +8170,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8190,17 +8194,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8210,12 +8214,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8285,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8377,24 +8381,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8404,7 +8408,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8453,12 +8457,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8562,7 +8566,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8605,32 +8609,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8638,7 +8646,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,17 +8670,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8682,17 +8690,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8720,32 +8728,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8753,7 +8765,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8777,27 +8789,27 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8835,32 +8847,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8868,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8892,37 +8908,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8950,12 +8966,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8983,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,10 +9007,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 13分钟参与校验</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9061,32 +9093,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9094,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,17 +9154,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9138,17 +9174,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9431,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9546,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9661,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9776,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9891,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10006,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10121,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10236,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10351,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10466,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,6 +10560,696 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,18 +3691,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5598,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6063,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6258,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6420,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6431,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6658,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6853,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7091,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7386,7 +7390,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7456,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7619,17 +7623,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7748,7 +7752,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7852,7 +7856,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7867,7 +7871,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7986,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8527,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8581,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8819,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8857,24 +8861,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8884,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8933,7 +8937,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8971,7 +8975,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8999,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9093,36 +9097,32 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9154,17 +9154,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9174,17 +9174,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9212,32 +9212,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9245,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,33 +9273,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9521,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9549,32 +9557,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9582,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,17 +9618,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9626,17 +9638,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9736,7 +9748,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9812,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9851,7 +9863,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9866,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10042,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10157,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10211,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10326,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10502,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10617,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10732,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10901,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11016,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11131,7 +11143,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11241,12 +11253,702 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2161,17 +2161,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,14 +3104,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6425,17 +6425,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7504,17 +7504,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8094,14 +8094,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8337,17 +8337,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9709,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,17 +9737,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9753,17 +9757,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9791,32 +9795,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9824,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9848,17 +9856,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9868,17 +9876,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9906,32 +9914,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9939,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9963,37 +9975,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10021,32 +10033,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10054,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10078,17 +10094,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10098,17 +10114,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10136,32 +10152,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10169,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10193,37 +10213,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10251,32 +10271,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10284,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10332,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10328,17 +10352,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10366,32 +10390,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10399,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10423,17 +10451,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10443,17 +10471,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10481,32 +10509,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10514,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,17 +10570,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10558,17 +10590,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10668,7 +10700,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10683,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10798,7 +10830,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10913,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10974,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11028,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11204,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11258,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11373,7 +11405,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11488,7 +11520,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11603,7 +11635,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11718,7 +11750,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11823,17 +11855,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11938,17 +11970,822 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>2/30</t>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2526,17 +2526,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2871,17 +2871,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3228,17 +3228,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3347,17 +3347,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6306,17 +6306,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7742,17 +7742,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7980,17 +7980,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8342,12 +8342,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8575,17 +8575,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8813,12 +8813,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10400,24 +10400,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10519,24 +10519,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10628,32 +10628,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10661,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10685,17 +10689,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10705,17 +10709,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10743,32 +10747,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10776,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,17 +10808,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10820,17 +10828,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10858,32 +10866,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10891,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10915,17 +10927,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10935,17 +10947,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10973,32 +10985,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11006,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,17 +11046,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11050,17 +11066,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11088,32 +11104,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11121,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11145,17 +11165,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11165,12 +11185,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11290,7 +11310,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11318,32 +11338,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11351,7 +11375,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,17 +11399,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11395,17 +11419,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11490,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11505,7 +11529,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11520,7 +11544,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11605,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11635,7 +11659,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11811,7 +11835,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11926,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11980,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12156,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12210,7 +12234,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12386,7 +12410,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12501,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12616,7 +12640,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12731,7 +12755,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12775,17 +12799,132 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB104" s="2" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="AC104" s="2" t="inlineStr">
-        <is>
-          <t>13/30</t>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9174,17 +9174,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9519,17 +9519,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9757,17 +9757,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11126,12 +11126,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11457,32 +11457,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11490,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11514,17 +11518,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11534,17 +11538,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11572,32 +11576,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11605,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11629,17 +11637,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11649,17 +11657,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11687,32 +11695,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11720,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11744,17 +11756,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11764,12 +11776,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11889,7 +11901,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11917,32 +11929,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11950,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,17 +11990,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11994,17 +12010,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12032,32 +12048,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12065,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12089,17 +12109,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12109,17 +12129,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12200,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12234,7 +12254,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12262,32 +12282,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12295,7 +12319,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,17 +12343,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12339,17 +12363,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12434,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12464,7 +12488,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12579,7 +12603,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12664,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12755,7 +12779,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12809,7 +12833,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12894,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12914,17 +12938,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东35路.xlsx
+++ b/data/export/2026-10-10-浦东35路.xlsx
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,17 +3109,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8099,17 +8099,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9995,17 +9995,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12401,32 +12401,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12434,7 +12438,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12458,17 +12462,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12478,17 +12482,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12516,32 +12520,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12549,7 +12557,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12573,17 +12581,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12593,17 +12601,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12631,32 +12639,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12664,7 +12676,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12688,17 +12700,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12708,17 +12720,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12791,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12833,7 +12845,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12906,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
